--- a/data/LLMSurveys_Configurations_harddata.xlsx
+++ b/data/LLMSurveys_Configurations_harddata.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Current\Work\LLMExpectations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB694DC-AD48-4BF8-A4B7-69E812E27EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31877668-8D3A-41EA-9844-DCFCF3C05979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1E49B1B9-B097-4895-90AA-09F755188166}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="24">
   <si>
     <t>UsdRub</t>
   </si>
@@ -97,6 +97,15 @@
   </si>
   <si>
     <t>LLama 70b (hard data, 7d)</t>
+  </si>
+  <si>
+    <t>QWEN 3.8 (news + hard data, 7d)</t>
+  </si>
+  <si>
+    <t>Gemma 3 27b (news + hard data, 7d)</t>
+  </si>
+  <si>
+    <t>LLama 70b (news + hard data, 7d)</t>
   </si>
 </sst>
 </file>
@@ -220,7 +229,67 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -551,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF250728-16E4-438D-A8DD-F8C642EF43D3}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="55.81640625" customWidth="1"/>
@@ -906,8 +975,137 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:K10">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+      <formula>"Да"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"Нет"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:K11">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+      <formula>"Да"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+      <formula>"Нет"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:K12">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"Да"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"Нет"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:K13">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Да"</formula>
     </cfRule>

--- a/data/LLMSurveys_Configurations_harddata.xlsx
+++ b/data/LLMSurveys_Configurations_harddata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Current\Work\LLMExpectations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31877668-8D3A-41EA-9844-DCFCF3C05979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE328D1B-C366-4BD0-A990-5FA0A248CAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1E49B1B9-B097-4895-90AA-09F755188166}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="36">
   <si>
     <t>UsdRub</t>
   </si>
@@ -106,6 +106,42 @@
   </si>
   <si>
     <t>LLama 70b (news + hard data, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_QWEN 3.8 (без RLMS без IE + ключ, -7d от Инфом)</t>
+  </si>
+  <si>
+    <t>Avg_QWEN 3.8 (news only, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_QWEN 3.8 (+news +rlms e, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_Gemma 3 27b (news only, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_Gemma 3 27b (+news +rlms e, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_LLama 70b (news only, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_LLama 70b (+news +rlms e, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_Gemma 3 27b (hard data, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_LLama 70b (hard data, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_QWEN 3.8 (news + hard data, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_Gemma 3 27b (news + hard data, 7d)</t>
+  </si>
+  <si>
+    <t>Avg_LLama 70b (news + hard data, 7d)</t>
   </si>
 </sst>
 </file>
@@ -229,47 +265,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -620,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF250728-16E4-438D-A8DD-F8C642EF43D3}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="55.81640625" customWidth="1"/>
@@ -1080,24 +1076,428 @@
         <v>10</v>
       </c>
     </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:K10">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
-      <formula>"Да"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
-      <formula>"Нет"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:K11">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
-      <formula>"Да"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>"Нет"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12:K12">
+  <conditionalFormatting sqref="B1:K13">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
@@ -1105,7 +1505,7 @@
       <formula>"Нет"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:K13">
+  <conditionalFormatting sqref="B14:K25">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
